--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97656</v>
+        <v>97661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910907</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129910978</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910907</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129910978</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910907</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129910978</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129910907</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129910913</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129910978</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 55399-2025 artfynd.xlsx
+++ b/artfynd/A 55399-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>129910907</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129910913</v>
+        <v>129910978</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Parlahöjden revlummer, Dlr</t>
+          <t>Parlahöjden spillkråka 2, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498160</v>
+        <v>498257</v>
       </c>
       <c r="R3" t="n">
-        <v>6692335</v>
+        <v>6692469</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,50 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129910978</v>
+        <v>129910913</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Parlahöjden spillkråka 2, Dlr</t>
+          <t>Parlahöjden revlummer, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498257</v>
+        <v>498160</v>
       </c>
       <c r="R4" t="n">
-        <v>6692469</v>
+        <v>6692335</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
